--- a/artfynd/A 51911-2025 artfynd.xlsx
+++ b/artfynd/A 51911-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>61865794</v>
+        <v>107421684</v>
       </c>
       <c r="B2" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stor-Vävelsjön, Jmt</t>
+          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>438563.833109336</v>
+        <v>438629</v>
       </c>
       <c r="R2" t="n">
-        <v>6954503.900533997</v>
+        <v>6954157</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-06-07</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-06-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,31 +756,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>gammal låga av tall</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>61865793</v>
+        <v>107421719</v>
       </c>
       <c r="B3" t="n">
-        <v>89545</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,37 +788,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1503</v>
+        <v>65</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stor-Vävelsjön, Jmt</t>
+          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>438558.5428689653</v>
+        <v>438594</v>
       </c>
       <c r="R3" t="n">
-        <v>6954515.930188312</v>
+        <v>6954527</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2016-06-07</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2016-06-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,69 +858,69 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>gammal låga avat</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>107421683</v>
+        <v>61865794</v>
       </c>
       <c r="B4" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
+          <t>Stor-Vävelsjön, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>438621.8004852728</v>
+        <v>438564</v>
       </c>
       <c r="R4" t="n">
-        <v>6954161.849763012</v>
+        <v>6954504</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +944,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-07-01</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-06-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-10-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-06-07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,27 +964,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>107421732</v>
+        <v>107421735</v>
       </c>
       <c r="B5" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>1049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>438614.7936918652</v>
+        <v>438651</v>
       </c>
       <c r="R5" t="n">
-        <v>6954550.675160038</v>
+        <v>6954439</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,21 +1044,11 @@
           <t>2022-07-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-10-30</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1110,7 +1060,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>silverved av tall</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1128,15 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>107421735</v>
+        <v>126514779</v>
       </c>
       <c r="B6" t="n">
-        <v>79433</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,14 +1109,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
+          <t>Dammkojan, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>438650.3962288959</v>
+        <v>438540</v>
       </c>
       <c r="R6" t="n">
-        <v>6954438.961373162</v>
+        <v>6954723</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,22 +1143,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-07-01</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-10-30</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1224,74 +1159,68 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>silverved av tall</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>107421734</v>
+        <v>61865793</v>
       </c>
       <c r="B7" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
+          <t>Stor-Vävelsjön, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>438702.9503783333</v>
+        <v>438559</v>
       </c>
       <c r="R7" t="n">
-        <v>6954546.740339271</v>
+        <v>6954516</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1315,22 +1244,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-07-01</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-06-07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-10-30</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-06-07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,40 +1260,30 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>silverved av tall</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>107421741</v>
+        <v>107421681</v>
       </c>
       <c r="B8" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1402,10 +1311,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>438738.5664514478</v>
+        <v>438587</v>
       </c>
       <c r="R8" t="n">
-        <v>6954262.477773088</v>
+        <v>6954173</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,19 +1344,9 @@
           <t>2022-07-01</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-10-30</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,19 +1373,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>107421738</v>
+        <v>107421683</v>
       </c>
       <c r="B9" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1514,10 +1408,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>438703.2441280495</v>
+        <v>438622</v>
       </c>
       <c r="R9" t="n">
-        <v>6954290.669413551</v>
+        <v>6954162</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1547,19 +1441,9 @@
           <t>2022-07-01</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-10-30</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,15 +1470,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>107421721</v>
+        <v>107421738</v>
       </c>
       <c r="B10" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1602,21 +1481,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1626,10 +1505,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>438569.9139253365</v>
+        <v>438703</v>
       </c>
       <c r="R10" t="n">
-        <v>6954484.972767045</v>
+        <v>6954291</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1659,21 +1538,11 @@
           <t>2022-07-01</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-10-30</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1682,11 +1551,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>brandstubbe</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1703,37 +1567,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>107421684</v>
+        <v>107421741</v>
       </c>
       <c r="B11" t="n">
-        <v>89633</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1743,10 +1602,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>438629.0658979806</v>
+        <v>438739</v>
       </c>
       <c r="R11" t="n">
-        <v>6954157.125164157</v>
+        <v>6954262</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1776,21 +1635,11 @@
           <t>2022-07-01</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-10-30</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1799,11 +1648,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>gammal låga av tall</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1820,15 +1664,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>107421733</v>
+        <v>107421744</v>
       </c>
       <c r="B12" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1836,21 +1675,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1860,10 +1699,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>438702.031634453</v>
+        <v>438841</v>
       </c>
       <c r="R12" t="n">
-        <v>6954546.757423052</v>
+        <v>6954266</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1893,21 +1732,11 @@
           <t>2022-07-01</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-10-30</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1916,11 +1745,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>brandstubbe</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1937,15 +1761,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>107421740</v>
+        <v>107421750</v>
       </c>
       <c r="B13" t="n">
-        <v>5426</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1953,21 +1772,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>101410</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1977,10 +1796,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>438735.1810123001</v>
+        <v>438729</v>
       </c>
       <c r="R13" t="n">
-        <v>6954278.143930548</v>
+        <v>6954130</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2010,21 +1829,11 @@
           <t>2022-07-01</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-10-30</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2033,11 +1842,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>gammal tall</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2054,15 +1858,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>107421747</v>
+        <v>61865795</v>
       </c>
       <c r="B14" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2070,37 +1869,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
+          <t>Stor-Vävelsjön, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>438882.7878667673</v>
+        <v>438648</v>
       </c>
       <c r="R14" t="n">
-        <v>6954233.183595491</v>
+        <v>6954781</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2124,22 +1923,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-07-01</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-06-07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-10-30</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-06-07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2150,36 +1939,26 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>silverved av tall</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>107421742</v>
+        <v>107421734</v>
       </c>
       <c r="B15" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2211,10 +1990,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>438744.5984677197</v>
+        <v>438703</v>
       </c>
       <c r="R15" t="n">
-        <v>6954265.578132508</v>
+        <v>6954547</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2244,19 +2023,9 @@
           <t>2022-07-01</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-10-30</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2288,37 +2057,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>107421719</v>
+        <v>107421742</v>
       </c>
       <c r="B16" t="n">
-        <v>89633</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>65</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2328,10 +2092,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>438594.1370163754</v>
+        <v>438744</v>
       </c>
       <c r="R16" t="n">
-        <v>6954527.19798374</v>
+        <v>6954265</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2361,21 +2125,11 @@
           <t>2022-07-01</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-10-30</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2387,7 +2141,7 @@
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>gammal låga avat</t>
+          <t>silverved av tall</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2405,37 +2159,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>107421681</v>
+        <v>107421740</v>
       </c>
       <c r="B17" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5495</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>101410</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2445,10 +2194,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>438586.6298105586</v>
+        <v>438735</v>
       </c>
       <c r="R17" t="n">
-        <v>6954173.519122583</v>
+        <v>6954278</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2478,21 +2227,11 @@
           <t>2022-07-01</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-10-30</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2501,6 +2240,11 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>gammal tall</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2517,15 +2261,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>107421731</v>
+        <v>126514862</v>
       </c>
       <c r="B18" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5495</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2533,34 +2272,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>101410</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
+          <t>Dammkojan, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>438547.348191208</v>
+        <v>438630</v>
       </c>
       <c r="R18" t="n">
-        <v>6954433.079432313</v>
+        <v>6954393</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2587,22 +2326,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-07-01</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-10-30</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>kläckhål</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2613,24 +2347,635 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>brandstubbe</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>107421721</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>438570</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6954485</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2022-10-30</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>brandstubbe</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>107421731</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>438548</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6954433</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2022-10-30</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>brandstubbe</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>107421732</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>438615</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6954550</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2022-10-30</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>brandstubbe</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>107421733</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>438702</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6954547</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2022-10-30</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>brandstubbe</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>107421746</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>438849</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6954263</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2022-10-30</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>brandstubbe</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>107421747</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>438883</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6954233</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2022-10-30</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>silverved av tall</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51911-2025 artfynd.xlsx
+++ b/artfynd/A 51911-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107421684</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107421719</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61865794</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107421735</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1176,6 +1201,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126514779</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1273,6 +1303,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61865793</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1370,6 +1405,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107421681</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1467,6 +1507,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107421683</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1564,6 +1609,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107421738</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1661,6 +1711,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107421741</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1758,6 +1813,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107421744</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1855,6 +1915,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107421750</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1952,6 +2017,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61865795</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2054,6 +2124,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107421734</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2156,6 +2231,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107421742</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2258,6 +2338,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107421740</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2364,6 +2449,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126514862</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2466,6 +2556,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107421721</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2568,6 +2663,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107421731</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2670,6 +2770,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107421732</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2772,6 +2877,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107421733</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2874,6 +2984,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107421746</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2976,8 +3091,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107421747</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 51911-2025 artfynd.xlsx
+++ b/artfynd/A 51911-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ24"/>
+  <dimension ref="A1:AZ40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -894,48 +894,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>61865794</v>
+        <v>135784585</v>
       </c>
       <c r="B4" t="n">
-        <v>78993</v>
+        <v>92294</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stor-Vävelsjön, Jmt</t>
+          <t>Börtnan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>438564</v>
+        <v>438682</v>
       </c>
       <c r="R4" t="n">
-        <v>6954504</v>
+        <v>6954438</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,12 +959,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2016-06-07</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2016-06-07</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,27 +979,27 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/61865794</t>
+          <t>https://artportalen.se/Sighting/135784585</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>107421735</v>
+        <v>61865794</v>
       </c>
       <c r="B5" t="n">
-        <v>81312</v>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,37 +1007,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1049</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
+          <t>Stor-Vävelsjön, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>438651</v>
+        <v>438564</v>
       </c>
       <c r="R5" t="n">
-        <v>6954439</v>
+        <v>6954504</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-07-01</t>
+          <t>2016-06-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-10-30</t>
+          <t>2016-06-07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1077,33 +1077,28 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>silverved av tall</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/107421735</t>
+          <t>https://artportalen.se/Sighting/61865794</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126514779</v>
+        <v>107421735</v>
       </c>
       <c r="B6" t="n">
         <v>81312</v>
@@ -1134,14 +1129,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Dammkojan, Jmt</t>
+          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>438540</v>
+        <v>438651</v>
       </c>
       <c r="R6" t="n">
-        <v>6954723</v>
+        <v>6954439</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,12 +1163,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2022-07-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2022-10-30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1184,73 +1179,74 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>silverved av tall</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126514779</t>
+          <t>https://artportalen.se/Sighting/107421735</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>61865793</v>
+        <v>126514779</v>
       </c>
       <c r="B7" t="n">
-        <v>92083</v>
+        <v>81312</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1503</v>
+        <v>1049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stor-Vävelsjön, Jmt</t>
+          <t>Dammkojan, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>438559</v>
+        <v>438540</v>
       </c>
       <c r="R7" t="n">
-        <v>6954516</v>
+        <v>6954723</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1274,12 +1270,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2016-06-07</t>
+          <t>2025-07-05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2016-06-07</t>
+          <t>2025-07-05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1294,65 +1290,69 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/61865793</t>
+          <t>https://artportalen.se/Sighting/126514779</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>107421681</v>
+        <v>61865793</v>
       </c>
       <c r="B8" t="n">
-        <v>93197</v>
+        <v>92083</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
+          <t>Stor-Vävelsjön, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>438587</v>
+        <v>438559</v>
       </c>
       <c r="R8" t="n">
-        <v>6954173</v>
+        <v>6954516</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1376,12 +1376,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-07-01</t>
+          <t>2016-06-07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-10-30</t>
+          <t>2016-06-07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1396,27 +1396,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/107421681</t>
+          <t>https://artportalen.se/Sighting/61865793</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>107421683</v>
+        <v>135784584</v>
       </c>
       <c r="B9" t="n">
-        <v>93197</v>
+        <v>91069</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1424,34 +1424,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
+          <t>Börtnan, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>438622</v>
+        <v>438677</v>
       </c>
       <c r="R9" t="n">
-        <v>6954162</v>
+        <v>6954431</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-07-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-10-30</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1498,27 +1498,27 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/107421683</t>
+          <t>https://artportalen.se/Sighting/135784584</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>107421738</v>
+        <v>135784589</v>
       </c>
       <c r="B10" t="n">
-        <v>93197</v>
+        <v>80557</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1526,34 +1526,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
+          <t>Börtnan, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>438703</v>
+        <v>438748</v>
       </c>
       <c r="R10" t="n">
-        <v>6954291</v>
+        <v>6954468</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1580,12 +1580,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-07-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-10-30</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1600,24 +1600,24 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/107421738</t>
+          <t>https://artportalen.se/Sighting/135784589</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>107421741</v>
+        <v>107421681</v>
       </c>
       <c r="B11" t="n">
         <v>93197</v>
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>438739</v>
+        <v>438587</v>
       </c>
       <c r="R11" t="n">
-        <v>6954262</v>
+        <v>6954173</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,13 +1713,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/107421741</t>
+          <t>https://artportalen.se/Sighting/107421681</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>107421744</v>
+        <v>107421683</v>
       </c>
       <c r="B12" t="n">
         <v>93197</v>
@@ -1754,10 +1754,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>438841</v>
+        <v>438622</v>
       </c>
       <c r="R12" t="n">
-        <v>6954266</v>
+        <v>6954162</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,13 +1815,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/107421744</t>
+          <t>https://artportalen.se/Sighting/107421683</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>107421750</v>
+        <v>107421738</v>
       </c>
       <c r="B13" t="n">
         <v>93197</v>
@@ -1856,10 +1856,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>438729</v>
+        <v>438703</v>
       </c>
       <c r="R13" t="n">
-        <v>6954130</v>
+        <v>6954291</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,16 +1917,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/107421750</t>
+          <t>https://artportalen.se/Sighting/107421738</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>61865795</v>
+        <v>107421741</v>
       </c>
       <c r="B14" t="n">
-        <v>78730</v>
+        <v>93197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1934,37 +1934,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stor-Vävelsjön, Jmt</t>
+          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>438648</v>
+        <v>438739</v>
       </c>
       <c r="R14" t="n">
-        <v>6954781</v>
+        <v>6954262</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1988,12 +1988,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2016-06-07</t>
+          <t>2022-07-01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2016-06-07</t>
+          <t>2022-10-30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2008,27 +2008,27 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/61865795</t>
+          <t>https://artportalen.se/Sighting/107421741</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>107421734</v>
+        <v>107421744</v>
       </c>
       <c r="B15" t="n">
-        <v>79946</v>
+        <v>93197</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,21 +2036,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2060,10 +2060,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>438703</v>
+        <v>438841</v>
       </c>
       <c r="R15" t="n">
-        <v>6954547</v>
+        <v>6954266</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2107,11 +2107,6 @@
       <c r="AG15" t="b">
         <v>0</v>
       </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>silverved av tall</t>
-        </is>
-      </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
@@ -2126,16 +2121,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/107421734</t>
+          <t>https://artportalen.se/Sighting/107421744</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>107421742</v>
+        <v>107421750</v>
       </c>
       <c r="B16" t="n">
-        <v>79946</v>
+        <v>93197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2143,21 +2138,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2167,10 +2162,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>438744</v>
+        <v>438729</v>
       </c>
       <c r="R16" t="n">
-        <v>6954265</v>
+        <v>6954130</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,11 +2209,6 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>silverved av tall</t>
-        </is>
-      </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
@@ -2233,16 +2223,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/107421742</t>
+          <t>https://artportalen.se/Sighting/107421750</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>107421740</v>
+        <v>135784588</v>
       </c>
       <c r="B17" t="n">
-        <v>5495</v>
+        <v>93345</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2250,34 +2240,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>101410</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
+          <t>Börtnan, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>438735</v>
+        <v>438730</v>
       </c>
       <c r="R17" t="n">
-        <v>6954278</v>
+        <v>6954455</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2304,12 +2294,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-07-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-10-30</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2320,36 +2310,31 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>gammal tall</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/107421740</t>
+          <t>https://artportalen.se/Sighting/135784588</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126514862</v>
+        <v>135784582</v>
       </c>
       <c r="B18" t="n">
-        <v>5495</v>
+        <v>91580</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2357,34 +2342,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>101410</v>
+        <v>5754</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Dammkojan, Jmt</t>
+          <t>Börtnan, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>438630</v>
+        <v>438600</v>
       </c>
       <c r="R18" t="n">
-        <v>6954393</v>
+        <v>6954452</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2411,17 +2396,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>kläckhål</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2436,66 +2416,62 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126514862</t>
+          <t>https://artportalen.se/Sighting/135784582</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>107421721</v>
+        <v>135784592</v>
       </c>
       <c r="B19" t="n">
-        <v>79085</v>
+        <v>79441</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
+          <t>Börtnan, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>438570</v>
+        <v>439130</v>
       </c>
       <c r="R19" t="n">
-        <v>6954485</v>
+        <v>6954594</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2522,12 +2498,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-07-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-10-30</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2538,36 +2514,31 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>brandstubbe</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/107421721</t>
+          <t>https://artportalen.se/Sighting/135784592</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>107421731</v>
+        <v>61865795</v>
       </c>
       <c r="B20" t="n">
-        <v>79085</v>
+        <v>78730</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2575,37 +2546,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
+          <t>Stor-Vävelsjön, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>438548</v>
+        <v>438648</v>
       </c>
       <c r="R20" t="n">
-        <v>6954433</v>
+        <v>6954781</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2629,12 +2600,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-07-01</t>
+          <t>2016-06-07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-10-30</t>
+          <t>2016-06-07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2645,36 +2616,31 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>brandstubbe</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/107421731</t>
+          <t>https://artportalen.se/Sighting/61865795</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>107421732</v>
+        <v>135784596</v>
       </c>
       <c r="B21" t="n">
-        <v>79085</v>
+        <v>78844</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2682,34 +2648,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
+          <t>Börtnan, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>438615</v>
+        <v>438857</v>
       </c>
       <c r="R21" t="n">
-        <v>6954550</v>
+        <v>6954400</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2736,12 +2702,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-07-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-10-30</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2752,36 +2718,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>brandstubbe</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/107421732</t>
+          <t>https://artportalen.se/Sighting/135784596</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>107421733</v>
+        <v>135784593</v>
       </c>
       <c r="B22" t="n">
-        <v>79085</v>
+        <v>79198</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2789,34 +2750,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
+          <t>Börtnan, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>438702</v>
+        <v>439130</v>
       </c>
       <c r="R22" t="n">
-        <v>6954547</v>
+        <v>6954502</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2843,12 +2804,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2022-07-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2022-10-30</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2859,36 +2820,31 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>brandstubbe</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/107421733</t>
+          <t>https://artportalen.se/Sighting/135784593</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>107421746</v>
+        <v>107421734</v>
       </c>
       <c r="B23" t="n">
-        <v>79085</v>
+        <v>79946</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2896,21 +2852,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2920,10 +2876,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>438849</v>
+        <v>438703</v>
       </c>
       <c r="R23" t="n">
-        <v>6954263</v>
+        <v>6954547</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2969,7 +2925,7 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>silverved av tall</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -2986,16 +2942,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/107421746</t>
+          <t>https://artportalen.se/Sighting/107421734</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>107421747</v>
+        <v>107421742</v>
       </c>
       <c r="B24" t="n">
-        <v>79917</v>
+        <v>79946</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3003,21 +2959,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3027,10 +2983,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>438883</v>
+        <v>438744</v>
       </c>
       <c r="R24" t="n">
-        <v>6954233</v>
+        <v>6954265</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3093,7 +3049,1683 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/107421742</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135784587</v>
+      </c>
+      <c r="B25" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Börtnan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>438706</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6954442</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784587</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135784590</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80561</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Börtnan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>438748</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6954468</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784590</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135784591</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78445</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Börtnan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>438754</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6954475</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784591</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135784594</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Börtnan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>438881</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6954380</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784594</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>107421740</v>
+      </c>
+      <c r="B29" t="n">
+        <v>5495</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>438735</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6954278</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2022-10-30</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>gammal tall</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107421740</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>126514862</v>
+      </c>
+      <c r="B30" t="n">
+        <v>5495</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Dammkojan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>438630</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6954393</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>kläckhål</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126514862</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135784580</v>
+      </c>
+      <c r="B31" t="n">
+        <v>108030</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>219933</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Kattfot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Antennaria dioica</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Gaertn.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Börtnan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>438580</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6954454</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784580</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135784581</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98142</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Börtnan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>438582</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6954454</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784581</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135784583</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99296</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Börtnan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>438597</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6954460</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784583</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>107421721</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>438570</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6954485</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2022-10-30</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>brandstubbe</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107421721</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>107421731</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>438548</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6954433</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2022-10-30</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>brandstubbe</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107421731</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>107421732</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>438615</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6954550</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2022-10-30</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>brandstubbe</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107421732</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>107421733</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>438702</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6954547</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2022-10-30</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>brandstubbe</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107421733</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>107421746</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>438849</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6954263</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2022-10-30</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>brandstubbe</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107421746</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>107421747</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>438883</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6954233</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2022-10-30</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>silverved av tall</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/107421747</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135784595</v>
+      </c>
+      <c r="B40" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Börtnan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>438855</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6954401</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784595</t>
         </is>
       </c>
     </row>
@@ -3122,6 +4754,22 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51911-2025 artfynd.xlsx
+++ b/artfynd/A 51911-2025 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>135784585</v>
       </c>
       <c r="B4" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>135784584</v>
       </c>
       <c r="B9" t="n">
-        <v>91069</v>
+        <v>91071</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>135784588</v>
       </c>
       <c r="B17" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>135784582</v>
       </c>
       <c r="B18" t="n">
-        <v>91580</v>
+        <v>91582</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>135784580</v>
       </c>
       <c r="B31" t="n">
-        <v>108030</v>
+        <v>108032</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>135784581</v>
       </c>
       <c r="B32" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>135784583</v>
       </c>
       <c r="B33" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 51911-2025 artfynd.xlsx
+++ b/artfynd/A 51911-2025 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>135784585</v>
       </c>
       <c r="B4" t="n">
-        <v>92296</v>
+        <v>92310</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>135784584</v>
       </c>
       <c r="B9" t="n">
-        <v>91071</v>
+        <v>91073</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>135784589</v>
       </c>
       <c r="B10" t="n">
-        <v>80557</v>
+        <v>80559</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>135784588</v>
       </c>
       <c r="B17" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>135784582</v>
       </c>
       <c r="B18" t="n">
-        <v>91582</v>
+        <v>91584</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>135784592</v>
       </c>
       <c r="B19" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>135784596</v>
       </c>
       <c r="B21" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>135784593</v>
       </c>
       <c r="B22" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>135784587</v>
       </c>
       <c r="B25" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         <v>135784590</v>
       </c>
       <c r="B26" t="n">
-        <v>80561</v>
+        <v>80563</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>135784591</v>
       </c>
       <c r="B27" t="n">
-        <v>78445</v>
+        <v>78447</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>135784594</v>
       </c>
       <c r="B28" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>135784580</v>
       </c>
       <c r="B31" t="n">
-        <v>108032</v>
+        <v>108055</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>135784581</v>
       </c>
       <c r="B32" t="n">
-        <v>98144</v>
+        <v>98161</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>135784583</v>
       </c>
       <c r="B33" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
         <v>135784595</v>
       </c>
       <c r="B40" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 51911-2025 artfynd.xlsx
+++ b/artfynd/A 51911-2025 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>135784585</v>
       </c>
       <c r="B4" t="n">
-        <v>92310</v>
+        <v>92311</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>135784584</v>
       </c>
       <c r="B9" t="n">
-        <v>91073</v>
+        <v>91074</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>135784589</v>
       </c>
       <c r="B10" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>135784588</v>
       </c>
       <c r="B17" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>135784582</v>
       </c>
       <c r="B18" t="n">
-        <v>91584</v>
+        <v>91585</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>135784592</v>
       </c>
       <c r="B19" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>135784596</v>
       </c>
       <c r="B21" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>135784593</v>
       </c>
       <c r="B22" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>135784587</v>
       </c>
       <c r="B25" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         <v>135784590</v>
       </c>
       <c r="B26" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>135784591</v>
       </c>
       <c r="B27" t="n">
-        <v>78447</v>
+        <v>78448</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>135784580</v>
       </c>
       <c r="B31" t="n">
-        <v>108055</v>
+        <v>108057</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>135784581</v>
       </c>
       <c r="B32" t="n">
-        <v>98161</v>
+        <v>98162</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>135784583</v>
       </c>
       <c r="B33" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
         <v>135784595</v>
       </c>
       <c r="B40" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 51911-2025 artfynd.xlsx
+++ b/artfynd/A 51911-2025 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>135784585</v>
       </c>
       <c r="B4" t="n">
-        <v>92311</v>
+        <v>92312</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>135784584</v>
       </c>
       <c r="B9" t="n">
-        <v>91074</v>
+        <v>91075</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>135784588</v>
       </c>
       <c r="B17" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>135784582</v>
       </c>
       <c r="B18" t="n">
-        <v>91585</v>
+        <v>91586</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>135784580</v>
       </c>
       <c r="B31" t="n">
-        <v>108057</v>
+        <v>108058</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>135784581</v>
       </c>
       <c r="B32" t="n">
-        <v>98162</v>
+        <v>98163</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>135784583</v>
       </c>
       <c r="B33" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 51911-2025 artfynd.xlsx
+++ b/artfynd/A 51911-2025 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>135784585</v>
       </c>
       <c r="B4" t="n">
-        <v>92312</v>
+        <v>92313</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>135784584</v>
       </c>
       <c r="B9" t="n">
-        <v>91075</v>
+        <v>91076</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>135784589</v>
       </c>
       <c r="B10" t="n">
-        <v>80560</v>
+        <v>80561</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>135784588</v>
       </c>
       <c r="B17" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>135784582</v>
       </c>
       <c r="B18" t="n">
-        <v>91586</v>
+        <v>91587</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>135784592</v>
       </c>
       <c r="B19" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>135784596</v>
       </c>
       <c r="B21" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>135784593</v>
       </c>
       <c r="B22" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>135784587</v>
       </c>
       <c r="B25" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         <v>135784590</v>
       </c>
       <c r="B26" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>135784591</v>
       </c>
       <c r="B27" t="n">
-        <v>78448</v>
+        <v>78449</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>135784594</v>
       </c>
       <c r="B28" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>135784580</v>
       </c>
       <c r="B31" t="n">
-        <v>108058</v>
+        <v>108059</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>135784581</v>
       </c>
       <c r="B32" t="n">
-        <v>98163</v>
+        <v>98164</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>135784583</v>
       </c>
       <c r="B33" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
         <v>135784595</v>
       </c>
       <c r="B40" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 51911-2025 artfynd.xlsx
+++ b/artfynd/A 51911-2025 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>135784585</v>
       </c>
       <c r="B4" t="n">
-        <v>92313</v>
+        <v>92319</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>135784584</v>
       </c>
       <c r="B9" t="n">
-        <v>91076</v>
+        <v>91082</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>135784589</v>
       </c>
       <c r="B10" t="n">
-        <v>80561</v>
+        <v>80565</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>135784588</v>
       </c>
       <c r="B17" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>135784582</v>
       </c>
       <c r="B18" t="n">
-        <v>91587</v>
+        <v>91593</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>135784592</v>
       </c>
       <c r="B19" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>135784596</v>
       </c>
       <c r="B21" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>135784593</v>
       </c>
       <c r="B22" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>135784587</v>
       </c>
       <c r="B25" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         <v>135784590</v>
       </c>
       <c r="B26" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>135784591</v>
       </c>
       <c r="B27" t="n">
-        <v>78449</v>
+        <v>78453</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>135784594</v>
       </c>
       <c r="B28" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>135784580</v>
       </c>
       <c r="B31" t="n">
-        <v>108059</v>
+        <v>108065</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>135784581</v>
       </c>
       <c r="B32" t="n">
-        <v>98164</v>
+        <v>98170</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>135784583</v>
       </c>
       <c r="B33" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
         <v>135784595</v>
       </c>
       <c r="B40" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 51911-2025 artfynd.xlsx
+++ b/artfynd/A 51911-2025 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>135784585</v>
       </c>
       <c r="B4" t="n">
-        <v>92319</v>
+        <v>92320</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>135784584</v>
       </c>
       <c r="B9" t="n">
-        <v>91082</v>
+        <v>91083</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>135784589</v>
       </c>
       <c r="B10" t="n">
-        <v>80565</v>
+        <v>80566</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>135784588</v>
       </c>
       <c r="B17" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>135784582</v>
       </c>
       <c r="B18" t="n">
-        <v>91593</v>
+        <v>91594</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>135784592</v>
       </c>
       <c r="B19" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>135784596</v>
       </c>
       <c r="B21" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>135784593</v>
       </c>
       <c r="B22" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>135784587</v>
       </c>
       <c r="B25" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         <v>135784590</v>
       </c>
       <c r="B26" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>135784591</v>
       </c>
       <c r="B27" t="n">
-        <v>78453</v>
+        <v>78454</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>135784594</v>
       </c>
       <c r="B28" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>135784580</v>
       </c>
       <c r="B31" t="n">
-        <v>108065</v>
+        <v>108066</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>135784581</v>
       </c>
       <c r="B32" t="n">
-        <v>98170</v>
+        <v>98171</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>135784583</v>
       </c>
       <c r="B33" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
         <v>135784595</v>
       </c>
       <c r="B40" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 51911-2025 artfynd.xlsx
+++ b/artfynd/A 51911-2025 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>135784585</v>
       </c>
       <c r="B4" t="n">
-        <v>92320</v>
+        <v>92326</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>135784584</v>
       </c>
       <c r="B9" t="n">
-        <v>91083</v>
+        <v>91089</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>135784589</v>
       </c>
       <c r="B10" t="n">
-        <v>80566</v>
+        <v>80570</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>135784588</v>
       </c>
       <c r="B17" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>135784582</v>
       </c>
       <c r="B18" t="n">
-        <v>91594</v>
+        <v>91600</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>135784592</v>
       </c>
       <c r="B19" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>135784596</v>
       </c>
       <c r="B21" t="n">
-        <v>78853</v>
+        <v>78857</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>135784593</v>
       </c>
       <c r="B22" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>135784587</v>
       </c>
       <c r="B25" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         <v>135784590</v>
       </c>
       <c r="B26" t="n">
-        <v>80570</v>
+        <v>80574</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>135784591</v>
       </c>
       <c r="B27" t="n">
-        <v>78454</v>
+        <v>78458</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>135784580</v>
       </c>
       <c r="B31" t="n">
-        <v>108066</v>
+        <v>108077</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>135784581</v>
       </c>
       <c r="B32" t="n">
-        <v>98171</v>
+        <v>98182</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>135784583</v>
       </c>
       <c r="B33" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
         <v>135784595</v>
       </c>
       <c r="B40" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 51911-2025 artfynd.xlsx
+++ b/artfynd/A 51911-2025 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>135784585</v>
       </c>
       <c r="B4" t="n">
-        <v>92326</v>
+        <v>92333</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>135784584</v>
       </c>
       <c r="B9" t="n">
-        <v>91089</v>
+        <v>91096</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>135784589</v>
       </c>
       <c r="B10" t="n">
-        <v>80570</v>
+        <v>80576</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>135784588</v>
       </c>
       <c r="B17" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>135784582</v>
       </c>
       <c r="B18" t="n">
-        <v>91600</v>
+        <v>91607</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>135784592</v>
       </c>
       <c r="B19" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>135784596</v>
       </c>
       <c r="B21" t="n">
-        <v>78857</v>
+        <v>78863</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>135784593</v>
       </c>
       <c r="B22" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>135784587</v>
       </c>
       <c r="B25" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         <v>135784590</v>
       </c>
       <c r="B26" t="n">
-        <v>80574</v>
+        <v>80580</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>135784591</v>
       </c>
       <c r="B27" t="n">
-        <v>78458</v>
+        <v>78464</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>135784594</v>
       </c>
       <c r="B28" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>135784580</v>
       </c>
       <c r="B31" t="n">
-        <v>108077</v>
+        <v>108090</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>135784581</v>
       </c>
       <c r="B32" t="n">
-        <v>98182</v>
+        <v>98195</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>135784583</v>
       </c>
       <c r="B33" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
         <v>135784595</v>
       </c>
       <c r="B40" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 51911-2025 artfynd.xlsx
+++ b/artfynd/A 51911-2025 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>135784585</v>
       </c>
       <c r="B4" t="n">
-        <v>92333</v>
+        <v>92334</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>135784584</v>
       </c>
       <c r="B9" t="n">
-        <v>91096</v>
+        <v>91097</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>135784588</v>
       </c>
       <c r="B17" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>135784582</v>
       </c>
       <c r="B18" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>135784580</v>
       </c>
       <c r="B31" t="n">
-        <v>108090</v>
+        <v>108091</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>135784581</v>
       </c>
       <c r="B32" t="n">
-        <v>98195</v>
+        <v>98196</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>135784583</v>
       </c>
       <c r="B33" t="n">
-        <v>99349</v>
+        <v>99350</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
